--- a/WebAPI/RepositoryCreator.xlsx
+++ b/WebAPI/RepositoryCreator.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/059199f8c4ccd322/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CHM\CHM-Trip-API\WebAPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{073D940B-EEBA-4723-A151-D5C97169D5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{836861F2-EAE3-4674-9F2B-7FB0EB7B5824}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81937BC-19FF-4BA4-BA77-BEAB04FA5C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{DFD0F04C-BF56-485D-96B4-F361DE0E5A50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{DFD0F04C-BF56-485D-96B4-F361DE0E5A50}"/>
   </bookViews>
   <sheets>
     <sheet name="Repositories" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Definitions</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Bottom repositorymanager constructor</t>
+  </si>
+  <si>
+    <t>Attachments</t>
   </si>
 </sst>
 </file>
@@ -449,11 +452,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79180A8F-D767-409B-B119-B432EA0F81B3}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
@@ -535,31 +538,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B7" si="0">"I"&amp;A3&amp;"Repository"</f>
+        <f t="shared" ref="B3:B8" si="0">"I"&amp;A3&amp;"Repository"</f>
         <v>ISlotsRepository</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C7" si="1" xml:space="preserve"> "public interface I"&amp;A3&amp;"Repository : IRepositoryBase&lt;"&amp;A3&amp;"&gt;{}"</f>
+        <f t="shared" ref="C3:C8" si="1" xml:space="preserve"> "public interface I"&amp;A3&amp;"Repository : IRepositoryBase&lt;"&amp;A3&amp;"&gt;{}"</f>
         <v>public interface ISlotsRepository : IRepositoryBase&lt;Slots&gt;{}</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D7" si="2">A3&amp;"Repository"</f>
+        <f t="shared" ref="D3:D8" si="2">A3&amp;"Repository"</f>
         <v>SlotsRepository</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E7" si="3">" public class "&amp;A3&amp;"Repository : RepositoryBase&lt;"&amp;A3&amp;"&gt;, "&amp;B3&amp;"{public "&amp;A3&amp;"Repository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}"</f>
+        <f t="shared" ref="E3:E8" si="3">" public class "&amp;A3&amp;"Repository : RepositoryBase&lt;"&amp;A3&amp;"&gt;, "&amp;B3&amp;"{public "&amp;A3&amp;"Repository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}"</f>
         <v xml:space="preserve"> public class SlotsRepository : RepositoryBase&lt;Slots&gt;, ISlotsRepository{public SlotsRepository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F7" si="4">" private readonly Lazy&lt;"&amp;B3&amp;"&gt; _"&amp;B3&amp;";"</f>
+        <f t="shared" ref="F3:F8" si="4">" private readonly Lazy&lt;"&amp;B3&amp;"&gt; _"&amp;B3&amp;";"</f>
         <v xml:space="preserve"> private readonly Lazy&lt;ISlotsRepository&gt; _ISlotsRepository;</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G7" si="5">"_"&amp;B3&amp;" = new Lazy&lt;"&amp;B3&amp;"&gt;(() =&gt; new "&amp;D3&amp;"(_context));"</f>
+        <f t="shared" ref="G3:G8" si="5">"_"&amp;B3&amp;" = new Lazy&lt;"&amp;B3&amp;"&gt;(() =&gt; new "&amp;D3&amp;"(_context));"</f>
         <v>_ISlotsRepository = new Lazy&lt;ISlotsRepository&gt;(() =&gt; new SlotsRepository(_context));</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H7" si="6">"        public "&amp;B3&amp;" "&amp;B3&amp;" =&gt; _"&amp;B3&amp;".Value;"</f>
+        <f t="shared" ref="H3:H8" si="6">"        public "&amp;B3&amp;" "&amp;B3&amp;" =&gt; _"&amp;B3&amp;".Value;"</f>
         <v xml:space="preserve">        public ISlotsRepository ISlotsRepository =&gt; _ISlotsRepository.Value;</v>
       </c>
       <c r="I3" s="3">
@@ -708,6 +711,39 @@
       </c>
       <c r="I7" s="3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>IAttachmentsRepository</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="1"/>
+        <v>public interface IAttachmentsRepository : IRepositoryBase&lt;Attachments&gt;{}</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="2"/>
+        <v>AttachmentsRepository</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> public class AttachmentsRepository : RepositoryBase&lt;Attachments&gt;, IAttachmentsRepository{public AttachmentsRepository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> private readonly Lazy&lt;IAttachmentsRepository&gt; _IAttachmentsRepository;</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="5"/>
+        <v>_IAttachmentsRepository = new Lazy&lt;IAttachmentsRepository&gt;(() =&gt; new AttachmentsRepository(_context));</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">        public IAttachmentsRepository IAttachmentsRepository =&gt; _IAttachmentsRepository.Value;</v>
       </c>
     </row>
   </sheetData>

--- a/WebAPI/RepositoryCreator.xlsx
+++ b/WebAPI/RepositoryCreator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CHM\CHM-Trip-API\WebAPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81937BC-19FF-4BA4-BA77-BEAB04FA5C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5524E646-5F1D-4313-AD29-0BD61F1596A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{DFD0F04C-BF56-485D-96B4-F361DE0E5A50}"/>
   </bookViews>
@@ -37,9 +37,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>Definitions</t>
-  </si>
-  <si>
     <t>Slots</t>
   </si>
   <si>
@@ -80,6 +77,9 @@
   </si>
   <si>
     <t>Attachments</t>
+  </si>
+  <si>
+    <t>Tx_Credit</t>
   </si>
 </sst>
 </file>
@@ -468,28 +468,28 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="I1" s="2">
         <v>0</v>
@@ -499,35 +499,35 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B2" t="str">
         <f>"I"&amp;A2&amp;"Repository"</f>
-        <v>IDefinitionsRepository</v>
+        <v>ITx_CreditRepository</v>
       </c>
       <c r="C2" t="str">
         <f xml:space="preserve"> "public interface I"&amp;A2&amp;"Repository : IRepositoryBase&lt;"&amp;A2&amp;"&gt;{}"</f>
-        <v>public interface IDefinitionsRepository : IRepositoryBase&lt;Definitions&gt;{}</v>
+        <v>public interface ITx_CreditRepository : IRepositoryBase&lt;Tx_Credit&gt;{}</v>
       </c>
       <c r="D2" t="str">
         <f>A2&amp;"Repository"</f>
-        <v>DefinitionsRepository</v>
+        <v>Tx_CreditRepository</v>
       </c>
       <c r="E2" t="str">
         <f>" public class "&amp;A2&amp;"Repository : RepositoryBase&lt;"&amp;A2&amp;"&gt;, "&amp;B2&amp;"{public "&amp;A2&amp;"Repository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}"</f>
-        <v xml:space="preserve"> public class DefinitionsRepository : RepositoryBase&lt;Definitions&gt;, IDefinitionsRepository{public DefinitionsRepository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}</v>
+        <v xml:space="preserve"> public class Tx_CreditRepository : RepositoryBase&lt;Tx_Credit&gt;, ITx_CreditRepository{public Tx_CreditRepository(DBContextProvider dBContextProvider) : base(dBContextProvider) { }}</v>
       </c>
       <c r="F2" t="str">
         <f>" private readonly Lazy&lt;"&amp;B2&amp;"&gt; _"&amp;B2&amp;";"</f>
-        <v xml:space="preserve"> private readonly Lazy&lt;IDefinitionsRepository&gt; _IDefinitionsRepository;</v>
+        <v xml:space="preserve"> private readonly Lazy&lt;ITx_CreditRepository&gt; _ITx_CreditRepository;</v>
       </c>
       <c r="G2" t="str">
         <f>"_"&amp;B2&amp;" = new Lazy&lt;"&amp;B2&amp;"&gt;(() =&gt; new "&amp;D2&amp;"(_context));"</f>
-        <v>_IDefinitionsRepository = new Lazy&lt;IDefinitionsRepository&gt;(() =&gt; new DefinitionsRepository(_context));</v>
+        <v>_ITx_CreditRepository = new Lazy&lt;ITx_CreditRepository&gt;(() =&gt; new Tx_CreditRepository(_context));</v>
       </c>
       <c r="H2" t="str">
         <f>"        public "&amp;B2&amp;" "&amp;B2&amp;" =&gt; _"&amp;B2&amp;".Value;"</f>
-        <v xml:space="preserve">        public IDefinitionsRepository IDefinitionsRepository =&gt; _IDefinitionsRepository.Value;</v>
+        <v xml:space="preserve">        public ITx_CreditRepository ITx_CreditRepository =&gt; _ITx_CreditRepository.Value;</v>
       </c>
       <c r="I2" s="3">
         <v>0</v>
@@ -535,7 +535,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="str">
         <f t="shared" ref="B3:B8" si="0">"I"&amp;A3&amp;"Repository"</f>
@@ -571,7 +571,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" si="0"/>
@@ -607,7 +607,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
@@ -643,7 +643,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
@@ -679,7 +679,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
@@ -715,7 +715,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
